--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NORTH_CAROLINA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NORTH_CAROLINA_2022.xlsx
@@ -1597,7 +1597,7 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>0.0009406296685663697</v>
+        <v>0.0009406296685663696</v>
       </c>
     </row>
     <row r="70">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C180">
@@ -5593,7 +5593,7 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>0.0009406296685663697</v>
+        <v>0.0009406296685663696</v>
       </c>
     </row>
     <row r="292">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C293">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C303">
@@ -6007,7 +6007,7 @@
         <v>17</v>
       </c>
       <c r="D314">
-        <v>0.0009406296685663697</v>
+        <v>0.0009406296685663696</v>
       </c>
     </row>
     <row r="315">
@@ -6889,7 +6889,7 @@
         <v>163</v>
       </c>
       <c r="D363">
-        <v>0.009018978586842251</v>
+        <v>0.009018978586842252</v>
       </c>
     </row>
     <row r="364">
@@ -11281,7 +11281,7 @@
         <v>17</v>
       </c>
       <c r="D607">
-        <v>0.0009406296685663697</v>
+        <v>0.0009406296685663696</v>
       </c>
     </row>
     <row r="608">
@@ -12901,7 +12901,7 @@
         <v>17</v>
       </c>
       <c r="D697">
-        <v>0.0009406296685663697</v>
+        <v>0.0009406296685663696</v>
       </c>
     </row>
     <row r="698">
@@ -15162,7 +15162,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C823">
@@ -15295,7 +15295,7 @@
         <v>17</v>
       </c>
       <c r="D830">
-        <v>0.0009406296685663697</v>
+        <v>0.0009406296685663696</v>
       </c>
     </row>
     <row r="831">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C867">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C868">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C875">
@@ -17149,7 +17149,7 @@
         <v>17</v>
       </c>
       <c r="D933">
-        <v>0.0009406296685663697</v>
+        <v>0.0009406296685663696</v>
       </c>
     </row>
     <row r="934">
@@ -17365,7 +17365,7 @@
         <v>17</v>
       </c>
       <c r="D945">
-        <v>0.0009406296685663697</v>
+        <v>0.0009406296685663696</v>
       </c>
     </row>
     <row r="946">
@@ -19579,7 +19579,7 @@
         <v>17</v>
       </c>
       <c r="D1068">
-        <v>0.0009406296685663697</v>
+        <v>0.0009406296685663696</v>
       </c>
     </row>
     <row r="1069">
@@ -21397,7 +21397,7 @@
         <v>17</v>
       </c>
       <c r="D1169">
-        <v>0.0009406296685663697</v>
+        <v>0.0009406296685663696</v>
       </c>
     </row>
     <row r="1170">
